--- a/reference/dictionaries/EE.xlsx
+++ b/reference/dictionaries/EE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Documents\Development\EHR-BSI\reference\dictionaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528EAF3B-86EB-4C1E-B077-50D9AAFD78DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E279AC-9E1B-4F03-91A6-71DE8EE35523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="800" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="400">
   <si>
     <t>raw_column_name</t>
   </si>
@@ -1729,6 +1729,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" customWidth="1"/>
+    <col min="2" max="2" width="34.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2092,8 +2096,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.26953125" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2507,11 +2515,11 @@
       <c r="A25" t="s">
         <v>138</v>
       </c>
-      <c r="B25" t="s">
-        <v>149</v>
+      <c r="B25">
+        <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
         <v>141</v>
@@ -2525,10 +2533,10 @@
         <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>141</v>
@@ -2542,10 +2550,10 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -2559,10 +2567,10 @@
         <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D28" t="s">
         <v>141</v>
@@ -2576,10 +2584,10 @@
         <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -2593,10 +2601,10 @@
         <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
         <v>141</v>
@@ -2610,10 +2618,10 @@
         <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -2627,10 +2635,10 @@
         <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
         <v>141</v>
@@ -2641,19 +2649,19 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -2661,7 +2669,7 @@
         <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
         <v>115</v>
@@ -2678,7 +2686,7 @@
         <v>164</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
         <v>115</v>
@@ -2695,7 +2703,7 @@
         <v>164</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
         <v>115</v>
@@ -2712,7 +2720,7 @@
         <v>164</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
         <v>115</v>
@@ -2729,7 +2737,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
         <v>115</v>
@@ -2746,7 +2754,7 @@
         <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
         <v>115</v>
@@ -2763,7 +2771,7 @@
         <v>164</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
         <v>115</v>
@@ -2780,10 +2788,10 @@
         <v>164</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
         <v>166</v>
@@ -2797,7 +2805,7 @@
         <v>164</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C42" t="s">
         <v>117</v>
@@ -2814,7 +2822,7 @@
         <v>164</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" t="s">
         <v>117</v>
@@ -2831,10 +2839,10 @@
         <v>164</v>
       </c>
       <c r="B44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
         <v>166</v>
@@ -2848,7 +2856,7 @@
         <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C45" t="s">
         <v>179</v>
@@ -2862,19 +2870,19 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -2882,7 +2890,7 @@
         <v>181</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C47" t="s">
         <v>182</v>
@@ -2899,10 +2907,10 @@
         <v>181</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D48" t="s">
         <v>183</v>
@@ -2916,10 +2924,10 @@
         <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
         <v>183</v>
@@ -2933,7 +2941,7 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="C50" t="s">
         <v>182</v>
@@ -2950,7 +2958,7 @@
         <v>181</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
         <v>182</v>
@@ -2967,7 +2975,7 @@
         <v>181</v>
       </c>
       <c r="B52" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
         <v>182</v>
@@ -2984,7 +2992,7 @@
         <v>181</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C53" t="s">
         <v>182</v>
@@ -3001,7 +3009,7 @@
         <v>181</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C54" t="s">
         <v>182</v>
@@ -3018,7 +3026,7 @@
         <v>181</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C55" t="s">
         <v>182</v>
@@ -3035,7 +3043,7 @@
         <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
         <v>182</v>
@@ -3052,7 +3060,7 @@
         <v>181</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C57" t="s">
         <v>182</v>
@@ -3069,7 +3077,7 @@
         <v>181</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C58" t="s">
         <v>182</v>
@@ -3086,7 +3094,7 @@
         <v>181</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C59" t="s">
         <v>182</v>
@@ -3103,7 +3111,7 @@
         <v>181</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C60" t="s">
         <v>182</v>
@@ -3120,7 +3128,7 @@
         <v>181</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
         <v>182</v>
@@ -3137,10 +3145,10 @@
         <v>181</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C62" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
         <v>183</v>
@@ -3151,19 +3159,19 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B63" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D63" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -3171,10 +3179,10 @@
         <v>190</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D64" t="s">
         <v>193</v>
@@ -3188,10 +3196,10 @@
         <v>190</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D65" t="s">
         <v>193</v>
@@ -3205,10 +3213,10 @@
         <v>190</v>
       </c>
       <c r="B66" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D66" t="s">
         <v>193</v>
@@ -3222,10 +3230,10 @@
         <v>190</v>
       </c>
       <c r="B67" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C67" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D67" t="s">
         <v>193</v>
@@ -3239,10 +3247,10 @@
         <v>190</v>
       </c>
       <c r="B68" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D68" t="s">
         <v>193</v>
@@ -3256,7 +3264,7 @@
         <v>190</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C69" t="s">
         <v>203</v>
@@ -3273,10 +3281,10 @@
         <v>190</v>
       </c>
       <c r="B70" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C70" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D70" t="s">
         <v>193</v>
@@ -3290,7 +3298,7 @@
         <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C71" t="s">
         <v>206</v>
@@ -3307,10 +3315,10 @@
         <v>190</v>
       </c>
       <c r="B72" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D72" t="s">
         <v>193</v>
@@ -3324,10 +3332,10 @@
         <v>190</v>
       </c>
       <c r="B73" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C73" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D73" t="s">
         <v>193</v>
@@ -3341,10 +3349,10 @@
         <v>190</v>
       </c>
       <c r="B74" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D74" t="s">
         <v>193</v>
@@ -3358,10 +3366,10 @@
         <v>190</v>
       </c>
       <c r="B75" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D75" t="s">
         <v>193</v>
@@ -3375,10 +3383,10 @@
         <v>190</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D76" t="s">
         <v>193</v>
@@ -3392,10 +3400,10 @@
         <v>190</v>
       </c>
       <c r="B77" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
         <v>193</v>
@@ -3409,10 +3417,10 @@
         <v>190</v>
       </c>
       <c r="B78" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C78" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D78" t="s">
         <v>193</v>
@@ -3426,10 +3434,10 @@
         <v>190</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C79" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D79" t="s">
         <v>193</v>
@@ -3443,10 +3451,10 @@
         <v>190</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D80" t="s">
         <v>193</v>
@@ -3460,10 +3468,10 @@
         <v>190</v>
       </c>
       <c r="B81" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D81" t="s">
         <v>193</v>
@@ -3477,10 +3485,10 @@
         <v>190</v>
       </c>
       <c r="B82" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D82" t="s">
         <v>193</v>
@@ -3494,10 +3502,10 @@
         <v>190</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D83" t="s">
         <v>193</v>
@@ -3511,10 +3519,10 @@
         <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C84" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D84" t="s">
         <v>193</v>
@@ -3528,10 +3536,10 @@
         <v>190</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D85" t="s">
         <v>193</v>
@@ -3545,10 +3553,10 @@
         <v>190</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C86" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D86" t="s">
         <v>193</v>
@@ -3562,10 +3570,10 @@
         <v>190</v>
       </c>
       <c r="B87" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C87" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D87" t="s">
         <v>193</v>
@@ -3579,10 +3587,10 @@
         <v>190</v>
       </c>
       <c r="B88" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D88" t="s">
         <v>193</v>
@@ -3596,10 +3604,10 @@
         <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C89" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D89" t="s">
         <v>193</v>
@@ -3613,10 +3621,10 @@
         <v>190</v>
       </c>
       <c r="B90" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C90" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D90" t="s">
         <v>193</v>
@@ -3630,10 +3638,10 @@
         <v>190</v>
       </c>
       <c r="B91" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D91" t="s">
         <v>193</v>
@@ -3647,10 +3655,10 @@
         <v>190</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D92" t="s">
         <v>193</v>
@@ -3664,10 +3672,10 @@
         <v>190</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D93" t="s">
         <v>193</v>
@@ -3681,10 +3689,10 @@
         <v>190</v>
       </c>
       <c r="B94" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D94" t="s">
         <v>193</v>
@@ -3698,10 +3706,10 @@
         <v>190</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D95" t="s">
         <v>193</v>
@@ -3715,10 +3723,10 @@
         <v>190</v>
       </c>
       <c r="B96" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C96" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D96" t="s">
         <v>193</v>
@@ -3732,10 +3740,10 @@
         <v>190</v>
       </c>
       <c r="B97" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C97" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D97" t="s">
         <v>193</v>
@@ -3749,10 +3757,10 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C98" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
         <v>193</v>
@@ -3766,10 +3774,10 @@
         <v>190</v>
       </c>
       <c r="B99" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C99" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D99" t="s">
         <v>193</v>
@@ -3783,10 +3791,10 @@
         <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C100" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D100" t="s">
         <v>193</v>
@@ -3800,10 +3808,10 @@
         <v>190</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C101" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D101" t="s">
         <v>193</v>
@@ -3817,10 +3825,10 @@
         <v>190</v>
       </c>
       <c r="B102" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C102" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D102" t="s">
         <v>193</v>
@@ -3834,10 +3842,10 @@
         <v>190</v>
       </c>
       <c r="B103" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C103" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D103" t="s">
         <v>193</v>
@@ -3851,10 +3859,10 @@
         <v>190</v>
       </c>
       <c r="B104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D104" t="s">
         <v>193</v>
@@ -3868,10 +3876,10 @@
         <v>190</v>
       </c>
       <c r="B105" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C105" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D105" t="s">
         <v>193</v>
@@ -3885,10 +3893,10 @@
         <v>190</v>
       </c>
       <c r="B106" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C106" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D106" t="s">
         <v>193</v>
@@ -3902,10 +3910,10 @@
         <v>190</v>
       </c>
       <c r="B107" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C107" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D107" t="s">
         <v>193</v>
@@ -3919,10 +3927,10 @@
         <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C108" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D108" t="s">
         <v>193</v>
@@ -3936,10 +3944,10 @@
         <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C109" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D109" t="s">
         <v>193</v>
@@ -3953,10 +3961,10 @@
         <v>190</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D110" t="s">
         <v>193</v>
@@ -3970,10 +3978,10 @@
         <v>190</v>
       </c>
       <c r="B111" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C111" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D111" t="s">
         <v>193</v>
@@ -3987,10 +3995,10 @@
         <v>190</v>
       </c>
       <c r="B112" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D112" t="s">
         <v>193</v>
@@ -4004,10 +4012,10 @@
         <v>190</v>
       </c>
       <c r="B113" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C113" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D113" t="s">
         <v>193</v>
@@ -4021,7 +4029,7 @@
         <v>190</v>
       </c>
       <c r="B114" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C114" t="s">
         <v>291</v>
@@ -4038,10 +4046,10 @@
         <v>190</v>
       </c>
       <c r="B115" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D115" t="s">
         <v>193</v>
@@ -4055,10 +4063,10 @@
         <v>190</v>
       </c>
       <c r="B116" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D116" t="s">
         <v>193</v>
@@ -4072,10 +4080,10 @@
         <v>190</v>
       </c>
       <c r="B117" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C117" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D117" t="s">
         <v>193</v>
@@ -4089,10 +4097,10 @@
         <v>190</v>
       </c>
       <c r="B118" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C118" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D118" t="s">
         <v>193</v>
@@ -4106,10 +4114,10 @@
         <v>190</v>
       </c>
       <c r="B119" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C119" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D119" t="s">
         <v>193</v>
@@ -4123,10 +4131,10 @@
         <v>190</v>
       </c>
       <c r="B120" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C120" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D120" t="s">
         <v>193</v>
@@ -4140,10 +4148,10 @@
         <v>190</v>
       </c>
       <c r="B121" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C121" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D121" t="s">
         <v>193</v>
@@ -4157,10 +4165,10 @@
         <v>190</v>
       </c>
       <c r="B122" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C122" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D122" t="s">
         <v>193</v>
@@ -4174,10 +4182,10 @@
         <v>190</v>
       </c>
       <c r="B123" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C123" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D123" t="s">
         <v>193</v>
@@ -4191,10 +4199,10 @@
         <v>190</v>
       </c>
       <c r="B124" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C124" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D124" t="s">
         <v>193</v>
@@ -4208,10 +4216,10 @@
         <v>190</v>
       </c>
       <c r="B125" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C125" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D125" t="s">
         <v>193</v>
@@ -4225,10 +4233,10 @@
         <v>190</v>
       </c>
       <c r="B126" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C126" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D126" t="s">
         <v>193</v>
@@ -4242,10 +4250,10 @@
         <v>190</v>
       </c>
       <c r="B127" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C127" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D127" t="s">
         <v>193</v>
@@ -4259,7 +4267,7 @@
         <v>190</v>
       </c>
       <c r="B128" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C128" t="s">
         <v>318</v>
@@ -4273,19 +4281,19 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>320</v>
+        <v>190</v>
       </c>
       <c r="B129" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C129" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D129" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E129" t="s">
-        <v>323</v>
+        <v>194</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
@@ -4293,10 +4301,10 @@
         <v>320</v>
       </c>
       <c r="B130" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
       <c r="C130" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D130" t="s">
         <v>194</v>
@@ -4310,7 +4318,7 @@
         <v>320</v>
       </c>
       <c r="B131" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C131" t="s">
         <v>324</v>
@@ -4327,7 +4335,7 @@
         <v>320</v>
       </c>
       <c r="B132" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C132" t="s">
         <v>324</v>
@@ -4344,10 +4352,10 @@
         <v>320</v>
       </c>
       <c r="B133" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C133" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D133" t="s">
         <v>194</v>
@@ -4361,10 +4369,10 @@
         <v>320</v>
       </c>
       <c r="B134" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C134" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D134" t="s">
         <v>194</v>
@@ -4378,10 +4386,10 @@
         <v>320</v>
       </c>
       <c r="B135" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C135" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D135" t="s">
         <v>194</v>
@@ -4395,10 +4403,10 @@
         <v>320</v>
       </c>
       <c r="B136" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D136" t="s">
         <v>194</v>
@@ -4412,10 +4420,10 @@
         <v>320</v>
       </c>
       <c r="B137" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="C137" t="s">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="D137" t="s">
         <v>194</v>
@@ -4429,7 +4437,7 @@
         <v>320</v>
       </c>
       <c r="B138" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C138" t="s">
         <v>209</v>
@@ -4446,7 +4454,7 @@
         <v>320</v>
       </c>
       <c r="B139" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C139" t="s">
         <v>209</v>
@@ -4463,10 +4471,10 @@
         <v>320</v>
       </c>
       <c r="B140" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C140" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D140" t="s">
         <v>194</v>
@@ -4480,10 +4488,10 @@
         <v>320</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>201</v>
       </c>
       <c r="C141" t="s">
-        <v>329</v>
+        <v>201</v>
       </c>
       <c r="D141" t="s">
         <v>194</v>
@@ -4497,10 +4505,10 @@
         <v>320</v>
       </c>
       <c r="B142" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="C142" t="s">
-        <v>285</v>
+        <v>329</v>
       </c>
       <c r="D142" t="s">
         <v>194</v>
@@ -4514,10 +4522,10 @@
         <v>320</v>
       </c>
       <c r="B143" t="s">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="C143" t="s">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="D143" t="s">
         <v>194</v>
@@ -4531,10 +4539,10 @@
         <v>320</v>
       </c>
       <c r="B144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D144" t="s">
         <v>194</v>
@@ -4548,10 +4556,10 @@
         <v>320</v>
       </c>
       <c r="B145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D145" t="s">
         <v>194</v>
@@ -4565,10 +4573,10 @@
         <v>320</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C146" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D146" t="s">
         <v>194</v>
@@ -4582,7 +4590,7 @@
         <v>320</v>
       </c>
       <c r="B147" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C147" t="s">
         <v>334</v>
@@ -4599,10 +4607,10 @@
         <v>320</v>
       </c>
       <c r="B148" t="s">
-        <v>231</v>
+        <v>335</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D148" t="s">
         <v>194</v>
@@ -4616,7 +4624,7 @@
         <v>320</v>
       </c>
       <c r="B149" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C149" t="s">
         <v>336</v>
@@ -4633,7 +4641,7 @@
         <v>320</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C150" t="s">
         <v>336</v>
@@ -4650,10 +4658,10 @@
         <v>320</v>
       </c>
       <c r="B151" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C151" t="s">
-        <v>229</v>
+        <v>336</v>
       </c>
       <c r="D151" t="s">
         <v>194</v>
@@ -4667,10 +4675,10 @@
         <v>320</v>
       </c>
       <c r="B152" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C152" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D152" t="s">
         <v>194</v>
@@ -4684,7 +4692,7 @@
         <v>320</v>
       </c>
       <c r="B153" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C153" t="s">
         <v>215</v>
@@ -4701,10 +4709,10 @@
         <v>320</v>
       </c>
       <c r="B154" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C154" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D154" t="s">
         <v>194</v>
@@ -4718,10 +4726,10 @@
         <v>320</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>227</v>
       </c>
       <c r="C155" t="s">
-        <v>338</v>
+        <v>227</v>
       </c>
       <c r="D155" t="s">
         <v>194</v>
@@ -4735,10 +4743,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
       <c r="C156" t="s">
-        <v>219</v>
+        <v>338</v>
       </c>
       <c r="D156" t="s">
         <v>194</v>
@@ -4752,10 +4760,10 @@
         <v>320</v>
       </c>
       <c r="B157" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C157" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D157" t="s">
         <v>194</v>
@@ -4769,10 +4777,10 @@
         <v>320</v>
       </c>
       <c r="B158" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C158" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D158" t="s">
         <v>194</v>
@@ -4786,10 +4794,10 @@
         <v>320</v>
       </c>
       <c r="B159" t="s">
-        <v>339</v>
+        <v>225</v>
       </c>
       <c r="C159" t="s">
-        <v>340</v>
+        <v>225</v>
       </c>
       <c r="D159" t="s">
         <v>194</v>
@@ -4803,10 +4811,10 @@
         <v>320</v>
       </c>
       <c r="B160" t="s">
-        <v>239</v>
+        <v>339</v>
       </c>
       <c r="C160" t="s">
-        <v>239</v>
+        <v>340</v>
       </c>
       <c r="D160" t="s">
         <v>194</v>
@@ -4820,10 +4828,10 @@
         <v>320</v>
       </c>
       <c r="B161" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C161" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D161" t="s">
         <v>194</v>
@@ -4837,10 +4845,10 @@
         <v>320</v>
       </c>
       <c r="B162" t="s">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="C162" t="s">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="D162" t="s">
         <v>194</v>
@@ -4854,10 +4862,10 @@
         <v>320</v>
       </c>
       <c r="B163" t="s">
-        <v>241</v>
+        <v>341</v>
       </c>
       <c r="C163" t="s">
-        <v>241</v>
+        <v>341</v>
       </c>
       <c r="D163" t="s">
         <v>194</v>
@@ -4871,10 +4879,10 @@
         <v>320</v>
       </c>
       <c r="B164" t="s">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="C164" t="s">
-        <v>342</v>
+        <v>241</v>
       </c>
       <c r="D164" t="s">
         <v>194</v>
@@ -4888,10 +4896,10 @@
         <v>320</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C165" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D165" t="s">
         <v>194</v>
@@ -4905,10 +4913,10 @@
         <v>320</v>
       </c>
       <c r="B166" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D166" t="s">
         <v>194</v>
@@ -4922,10 +4930,10 @@
         <v>320</v>
       </c>
       <c r="B167" t="s">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="C167" t="s">
-        <v>245</v>
+        <v>345</v>
       </c>
       <c r="D167" t="s">
         <v>194</v>
@@ -4939,10 +4947,10 @@
         <v>320</v>
       </c>
       <c r="B168" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C168" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D168" t="s">
         <v>194</v>
@@ -4956,10 +4964,10 @@
         <v>320</v>
       </c>
       <c r="B169" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C169" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D169" t="s">
         <v>194</v>
@@ -4973,10 +4981,10 @@
         <v>320</v>
       </c>
       <c r="B170" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C170" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D170" t="s">
         <v>194</v>
@@ -4990,10 +4998,10 @@
         <v>320</v>
       </c>
       <c r="B171" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="C171" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
       <c r="D171" t="s">
         <v>194</v>
@@ -5007,10 +5015,10 @@
         <v>320</v>
       </c>
       <c r="B172" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C172" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D172" t="s">
         <v>194</v>
@@ -5024,10 +5032,10 @@
         <v>320</v>
       </c>
       <c r="B173" t="s">
-        <v>253</v>
+        <v>347</v>
       </c>
       <c r="C173" t="s">
-        <v>253</v>
+        <v>347</v>
       </c>
       <c r="D173" t="s">
         <v>194</v>
@@ -5041,10 +5049,10 @@
         <v>320</v>
       </c>
       <c r="B174" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C174" t="s">
-        <v>348</v>
+        <v>253</v>
       </c>
       <c r="D174" t="s">
         <v>194</v>
@@ -5058,10 +5066,10 @@
         <v>320</v>
       </c>
       <c r="B175" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C175" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="D175" t="s">
         <v>194</v>
@@ -5075,10 +5083,10 @@
         <v>320</v>
       </c>
       <c r="B176" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D176" t="s">
         <v>194</v>
@@ -5092,10 +5100,10 @@
         <v>320</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>349</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
         <v>194</v>
@@ -5109,10 +5117,10 @@
         <v>320</v>
       </c>
       <c r="B178" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C178" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D178" t="s">
         <v>194</v>
@@ -5126,10 +5134,10 @@
         <v>320</v>
       </c>
       <c r="B179" t="s">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="C179" t="s">
-        <v>261</v>
+        <v>350</v>
       </c>
       <c r="D179" t="s">
         <v>194</v>
@@ -5143,10 +5151,10 @@
         <v>320</v>
       </c>
       <c r="B180" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C180" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D180" t="s">
         <v>194</v>
@@ -5160,10 +5168,10 @@
         <v>320</v>
       </c>
       <c r="B181" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C181" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D181" t="s">
         <v>194</v>
@@ -5177,10 +5185,10 @@
         <v>320</v>
       </c>
       <c r="B182" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C182" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D182" t="s">
         <v>194</v>
@@ -5194,10 +5202,10 @@
         <v>320</v>
       </c>
       <c r="B183" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C183" t="s">
-        <v>351</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
         <v>194</v>
@@ -5211,10 +5219,10 @@
         <v>320</v>
       </c>
       <c r="B184" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C184" t="s">
-        <v>273</v>
+        <v>351</v>
       </c>
       <c r="D184" t="s">
         <v>194</v>
@@ -5228,10 +5236,10 @@
         <v>320</v>
       </c>
       <c r="B185" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C185" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D185" t="s">
         <v>194</v>
@@ -5245,10 +5253,10 @@
         <v>320</v>
       </c>
       <c r="B186" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C186" t="s">
-        <v>353</v>
+        <v>275</v>
       </c>
       <c r="D186" t="s">
         <v>194</v>
@@ -5262,10 +5270,10 @@
         <v>320</v>
       </c>
       <c r="B187" t="s">
-        <v>277</v>
+        <v>352</v>
       </c>
       <c r="C187" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="D187" t="s">
         <v>194</v>
@@ -5279,10 +5287,10 @@
         <v>320</v>
       </c>
       <c r="B188" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C188" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
       <c r="D188" t="s">
         <v>194</v>
@@ -5296,10 +5304,10 @@
         <v>320</v>
       </c>
       <c r="B189" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="C189" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D189" t="s">
         <v>194</v>
@@ -5313,10 +5321,10 @@
         <v>320</v>
       </c>
       <c r="B190" t="s">
-        <v>281</v>
+        <v>355</v>
       </c>
       <c r="C190" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D190" t="s">
         <v>194</v>
@@ -5330,10 +5338,10 @@
         <v>320</v>
       </c>
       <c r="B191" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C191" t="s">
-        <v>271</v>
+        <v>356</v>
       </c>
       <c r="D191" t="s">
         <v>194</v>
@@ -5347,10 +5355,10 @@
         <v>320</v>
       </c>
       <c r="B192" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C192" t="s">
-        <v>357</v>
+        <v>271</v>
       </c>
       <c r="D192" t="s">
         <v>194</v>
@@ -5364,10 +5372,10 @@
         <v>320</v>
       </c>
       <c r="B193" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C193" t="s">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="D193" t="s">
         <v>194</v>
@@ -5381,10 +5389,10 @@
         <v>320</v>
       </c>
       <c r="B194" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C194" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D194" t="s">
         <v>194</v>
@@ -5398,10 +5406,10 @@
         <v>320</v>
       </c>
       <c r="B195" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C195" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="D195" t="s">
         <v>194</v>
@@ -5415,10 +5423,10 @@
         <v>320</v>
       </c>
       <c r="B196" t="s">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="C196" t="s">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="D196" t="s">
         <v>194</v>
@@ -5432,10 +5440,10 @@
         <v>320</v>
       </c>
       <c r="B197" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="C197" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="D197" t="s">
         <v>194</v>
@@ -5449,10 +5457,10 @@
         <v>320</v>
       </c>
       <c r="B198" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C198" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D198" t="s">
         <v>194</v>
@@ -5466,10 +5474,10 @@
         <v>320</v>
       </c>
       <c r="B199" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C199" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D199" t="s">
         <v>194</v>
@@ -5483,10 +5491,10 @@
         <v>320</v>
       </c>
       <c r="B200" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="C200" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="D200" t="s">
         <v>194</v>
@@ -5500,10 +5508,10 @@
         <v>320</v>
       </c>
       <c r="B201" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C201" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D201" t="s">
         <v>194</v>
@@ -5517,10 +5525,10 @@
         <v>320</v>
       </c>
       <c r="B202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C202" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D202" t="s">
         <v>194</v>
@@ -5534,10 +5542,10 @@
         <v>320</v>
       </c>
       <c r="B203" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="C203" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="D203" t="s">
         <v>194</v>
@@ -5551,10 +5559,10 @@
         <v>320</v>
       </c>
       <c r="B204" t="s">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="C204" t="s">
-        <v>362</v>
+        <v>325</v>
       </c>
       <c r="D204" t="s">
         <v>194</v>
@@ -5568,10 +5576,10 @@
         <v>320</v>
       </c>
       <c r="B205" t="s">
-        <v>363</v>
+        <v>291</v>
       </c>
       <c r="C205" t="s">
-        <v>318</v>
+        <v>362</v>
       </c>
       <c r="D205" t="s">
         <v>194</v>
@@ -5585,7 +5593,7 @@
         <v>320</v>
       </c>
       <c r="B206" t="s">
-        <v>318</v>
+        <v>363</v>
       </c>
       <c r="C206" t="s">
         <v>318</v>
@@ -5602,10 +5610,10 @@
         <v>320</v>
       </c>
       <c r="B207" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="C207" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D207" t="s">
         <v>194</v>
@@ -5619,10 +5627,10 @@
         <v>320</v>
       </c>
       <c r="B208" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C208" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D208" t="s">
         <v>194</v>
@@ -5636,10 +5644,10 @@
         <v>320</v>
       </c>
       <c r="B209" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C209" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="D209" t="s">
         <v>194</v>
@@ -5653,10 +5661,10 @@
         <v>320</v>
       </c>
       <c r="B210" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C210" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D210" t="s">
         <v>194</v>
@@ -5670,10 +5678,10 @@
         <v>320</v>
       </c>
       <c r="B211" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="C211" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="D211" t="s">
         <v>194</v>
@@ -5687,10 +5695,10 @@
         <v>320</v>
       </c>
       <c r="B212" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="C212" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="D212" t="s">
         <v>194</v>
@@ -5704,10 +5712,10 @@
         <v>320</v>
       </c>
       <c r="B213" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C213" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D213" t="s">
         <v>194</v>
@@ -5721,10 +5729,10 @@
         <v>320</v>
       </c>
       <c r="B214" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C214" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D214" t="s">
         <v>194</v>
@@ -5738,10 +5746,10 @@
         <v>320</v>
       </c>
       <c r="B215" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C215" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="D215" t="s">
         <v>194</v>
@@ -5755,7 +5763,7 @@
         <v>320</v>
       </c>
       <c r="B216" t="s">
-        <v>366</v>
+        <v>316</v>
       </c>
       <c r="C216" t="s">
         <v>365</v>
@@ -5769,19 +5777,19 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="B217" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C217" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D217" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="E217" t="s">
-        <v>84</v>
+        <v>323</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
@@ -5789,7 +5797,7 @@
         <v>367</v>
       </c>
       <c r="B218" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C218" t="s">
         <v>369</v>
@@ -5806,7 +5814,7 @@
         <v>367</v>
       </c>
       <c r="B219" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C219" t="s">
         <v>369</v>
@@ -5823,10 +5831,10 @@
         <v>367</v>
       </c>
       <c r="B220" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C220" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D220" t="s">
         <v>82</v>
@@ -5840,7 +5848,7 @@
         <v>367</v>
       </c>
       <c r="B221" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C221" t="s">
         <v>373</v>
@@ -5857,7 +5865,7 @@
         <v>367</v>
       </c>
       <c r="B222" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C222" t="s">
         <v>373</v>
@@ -5874,7 +5882,7 @@
         <v>367</v>
       </c>
       <c r="B223" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C223" t="s">
         <v>373</v>
@@ -5891,10 +5899,10 @@
         <v>367</v>
       </c>
       <c r="B224" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C224" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D224" t="s">
         <v>82</v>
@@ -5908,7 +5916,7 @@
         <v>367</v>
       </c>
       <c r="B225" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C225" t="s">
         <v>378</v>
@@ -5925,7 +5933,7 @@
         <v>367</v>
       </c>
       <c r="B226" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C226" t="s">
         <v>378</v>
@@ -5942,7 +5950,7 @@
         <v>367</v>
       </c>
       <c r="B227" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C227" t="s">
         <v>378</v>
@@ -5959,7 +5967,7 @@
         <v>367</v>
       </c>
       <c r="B228" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C228" t="s">
         <v>378</v>
@@ -5976,7 +5984,7 @@
         <v>367</v>
       </c>
       <c r="B229" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C229" t="s">
         <v>378</v>
@@ -5993,7 +6001,7 @@
         <v>367</v>
       </c>
       <c r="B230" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C230" t="s">
         <v>378</v>
@@ -6010,7 +6018,7 @@
         <v>367</v>
       </c>
       <c r="B231" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C231" t="s">
         <v>378</v>
@@ -6027,7 +6035,7 @@
         <v>367</v>
       </c>
       <c r="B232" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C232" t="s">
         <v>378</v>
@@ -6044,7 +6052,7 @@
         <v>367</v>
       </c>
       <c r="B233" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C233" t="s">
         <v>378</v>
@@ -6061,7 +6069,7 @@
         <v>367</v>
       </c>
       <c r="B234" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C234" t="s">
         <v>378</v>
@@ -6078,7 +6086,7 @@
         <v>367</v>
       </c>
       <c r="B235" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C235" t="s">
         <v>378</v>
@@ -6095,7 +6103,7 @@
         <v>367</v>
       </c>
       <c r="B236" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C236" t="s">
         <v>378</v>
@@ -6112,7 +6120,7 @@
         <v>367</v>
       </c>
       <c r="B237" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C237" t="s">
         <v>378</v>
@@ -6129,10 +6137,10 @@
         <v>367</v>
       </c>
       <c r="B238" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C238" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="D238" t="s">
         <v>82</v>
@@ -6143,19 +6151,19 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="B239" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C239" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D239" t="s">
         <v>82</v>
       </c>
       <c r="E239" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
@@ -6163,7 +6171,7 @@
         <v>394</v>
       </c>
       <c r="B240" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C240" t="s">
         <v>395</v>
@@ -6180,10 +6188,10 @@
         <v>394</v>
       </c>
       <c r="B241" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C241" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D241" t="s">
         <v>82</v>
@@ -6197,10 +6205,10 @@
         <v>394</v>
       </c>
       <c r="B242" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C242" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D242" t="s">
         <v>82</v>
@@ -6214,10 +6222,10 @@
         <v>394</v>
       </c>
       <c r="B243" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C243" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D243" t="s">
         <v>82</v>
@@ -6231,10 +6239,10 @@
         <v>394</v>
       </c>
       <c r="B244" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C244" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D244" t="s">
         <v>82</v>
@@ -6248,10 +6256,10 @@
         <v>394</v>
       </c>
       <c r="B245" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C245" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D245" t="s">
         <v>82</v>
@@ -6265,10 +6273,10 @@
         <v>394</v>
       </c>
       <c r="B246" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C246" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D246" t="s">
         <v>82</v>
@@ -6282,7 +6290,7 @@
         <v>394</v>
       </c>
       <c r="B247" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C247" t="s">
         <v>399</v>
@@ -6299,10 +6307,10 @@
         <v>394</v>
       </c>
       <c r="B248" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C248" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D248" t="s">
         <v>82</v>
@@ -6316,10 +6324,10 @@
         <v>394</v>
       </c>
       <c r="B249" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C249" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D249" t="s">
         <v>82</v>
@@ -6333,7 +6341,7 @@
         <v>394</v>
       </c>
       <c r="B250" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C250" t="s">
         <v>396</v>
@@ -6350,7 +6358,7 @@
         <v>394</v>
       </c>
       <c r="B251" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C251" t="s">
         <v>396</v>
@@ -6367,10 +6375,10 @@
         <v>394</v>
       </c>
       <c r="B252" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C252" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D252" t="s">
         <v>82</v>
@@ -6384,7 +6392,7 @@
         <v>394</v>
       </c>
       <c r="B253" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C253" t="s">
         <v>398</v>
@@ -6401,7 +6409,7 @@
         <v>394</v>
       </c>
       <c r="B254" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C254" t="s">
         <v>398</v>
@@ -6418,10 +6426,10 @@
         <v>394</v>
       </c>
       <c r="B255" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C255" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D255" t="s">
         <v>82</v>
@@ -6435,10 +6443,10 @@
         <v>394</v>
       </c>
       <c r="B256" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C256" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D256" t="s">
         <v>82</v>
@@ -6452,10 +6460,10 @@
         <v>394</v>
       </c>
       <c r="B257" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C257" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D257" t="s">
         <v>82</v>
@@ -6469,10 +6477,10 @@
         <v>394</v>
       </c>
       <c r="B258" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C258" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D258" t="s">
         <v>82</v>
@@ -6486,7 +6494,7 @@
         <v>394</v>
       </c>
       <c r="B259" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C259" t="s">
         <v>396</v>
@@ -6503,15 +6511,32 @@
         <v>394</v>
       </c>
       <c r="B260" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C260" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D260" t="s">
         <v>82</v>
       </c>
       <c r="E260" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>394</v>
+      </c>
+      <c r="B261" t="s">
+        <v>392</v>
+      </c>
+      <c r="C261" t="s">
+        <v>395</v>
+      </c>
+      <c r="D261" t="s">
+        <v>82</v>
+      </c>
+      <c r="E261" t="s">
         <v>89</v>
       </c>
     </row>

--- a/reference/dictionaries/EE.xlsx
+++ b/reference/dictionaries/EE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Documents\Development\EHR-BSI\reference\dictionaries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Documents\Development\EHR-BSI-2026\reference\dictionaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528EAF3B-86EB-4C1E-B077-50D9AAFD78DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC6EC64-8FA9-4F9C-A665-6ABCD9EF59B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="800" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="402">
   <si>
     <t>raw_column_name</t>
   </si>
@@ -30,9 +30,6 @@
     <t>standard_column_name</t>
   </si>
   <si>
-    <t>PATIENT_ID_HASH</t>
-  </si>
-  <si>
     <t>PatientId</t>
   </si>
   <si>
@@ -48,9 +45,6 @@
     <t>Sex</t>
   </si>
   <si>
-    <t>L1_PROC_TIME (sample collection date)</t>
-  </si>
-  <si>
     <t>L1_PROC_ARTICLE_CODE_NAME</t>
   </si>
   <si>
@@ -75,10 +69,6 @@
     <t>sensitivityTest_noncdm</t>
   </si>
   <si>
-    <t>L3_RSLT_CODE_NAME
-(SIR)</t>
-  </si>
-  <si>
     <t>sensitivityResult_noncdm</t>
   </si>
   <si>
@@ -94,45 +84,24 @@
     <t>sensitivityValue_noncdm</t>
   </si>
   <si>
-    <t>SAMPLE_CONTEINER_ID (Isolate ID)</t>
-  </si>
-  <si>
     <t>IsolateId</t>
   </si>
   <si>
-    <t>Hosital ID</t>
-  </si>
-  <si>
     <t>HospitalId</t>
   </si>
   <si>
-    <t>STAT_EPICRISIS_CASE_START (admission date)</t>
-  </si>
-  <si>
     <t>DateOfHospitalAdmission</t>
   </si>
   <si>
-    <t>STAT_EPICRISIS_CASE_END (discharge date)</t>
-  </si>
-  <si>
     <t>DateOfHospitalDischarge</t>
   </si>
   <si>
-    <t>Unit ID</t>
-  </si>
-  <si>
     <t>UnitSpecialtyShort</t>
   </si>
   <si>
-    <t>BED_START_TIME (unit admission date)</t>
-  </si>
-  <si>
     <t>DateOfAdmissionCurrentWard</t>
   </si>
   <si>
-    <t>BED_END_TIME (unit discharge date)</t>
-  </si>
-  <si>
     <t>DateOfDischargeCurrentWard</t>
   </si>
   <si>
@@ -1223,6 +1192,42 @@
   </si>
   <si>
     <t>EE009</t>
+  </si>
+  <si>
+    <t>PATIENT_ID</t>
+  </si>
+  <si>
+    <t>Lab ID</t>
+  </si>
+  <si>
+    <t>LaboratoryId</t>
+  </si>
+  <si>
+    <t>Hospital ID</t>
+  </si>
+  <si>
+    <t>CASE_START</t>
+  </si>
+  <si>
+    <t>CASE_END</t>
+  </si>
+  <si>
+    <t>BED_START_TIME</t>
+  </si>
+  <si>
+    <t>BED_END_TIME</t>
+  </si>
+  <si>
+    <t>UNIT ID</t>
+  </si>
+  <si>
+    <t>L1_PROC_TIME</t>
+  </si>
+  <si>
+    <t>SAMPLE_CONTEINER_ID</t>
+  </si>
+  <si>
+    <t>L3_RSLT_CODE_NAME</t>
   </si>
 </sst>
 </file>
@@ -1556,8 +1561,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="35.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1569,154 +1577,162 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>399</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>401</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>400</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>393</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>394</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>395</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>398</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>396</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>397</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>391</v>
+      </c>
+      <c r="B21" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -1732,356 +1748,356 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2097,4422 +2113,4422 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
         <v>103</v>
       </c>
-      <c r="B7" t="s">
-        <v>113</v>
-      </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C25" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E37" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B40" t="s">
         <v>164</v>
       </c>
-      <c r="B40" t="s">
-        <v>174</v>
-      </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C45" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E45" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" t="s">
         <v>172</v>
       </c>
-      <c r="C46" t="s">
-        <v>182</v>
-      </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B47" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C50" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C53" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D55" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
         <v>174</v>
-      </c>
-      <c r="C56" t="s">
-        <v>182</v>
-      </c>
-      <c r="D56" t="s">
-        <v>183</v>
-      </c>
-      <c r="E56" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E58" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E59" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E60" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E61" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
+        <v>163</v>
+      </c>
+      <c r="C62" t="s">
+        <v>177</v>
+      </c>
+      <c r="D62" t="s">
         <v>173</v>
       </c>
-      <c r="C62" t="s">
-        <v>187</v>
-      </c>
-      <c r="D62" t="s">
-        <v>183</v>
-      </c>
       <c r="E62" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B63" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D63" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E63" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D64" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B65" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D65" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B66" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C66" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D66" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>180</v>
+      </c>
+      <c r="B67" t="s">
         <v>190</v>
       </c>
-      <c r="B67" t="s">
-        <v>200</v>
-      </c>
       <c r="C67" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D67" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B68" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D68" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D69" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E69" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C70" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D70" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B71" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B72" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C72" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B74" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B75" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B76" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D76" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B77" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D77" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E77" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B78" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C78" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D78" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C79" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D79" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E79" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D80" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B81" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C81" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E81" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B82" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C82" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E82" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C83" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D83" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E83" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C84" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D85" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E85" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E86" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B87" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C87" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E87" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B88" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C88" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D88" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C89" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E89" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B90" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C90" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D90" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E90" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C91" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D91" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D92" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E92" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C93" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B94" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C94" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D94" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E94" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C95" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D95" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E95" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B96" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C96" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D96" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E96" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C97" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E97" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B98" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C98" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D98" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C99" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D99" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E99" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C100" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D100" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C101" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E101" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C102" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B103" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C103" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D103" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E103" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B104" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C104" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D104" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B105" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C105" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B106" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C106" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D106" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E106" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B107" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C107" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B108" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C108" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D108" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B109" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C109" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D109" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D110" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C111" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D111" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E111" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B112" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D112" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E112" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B113" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C113" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D113" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E113" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C114" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D114" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C115" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D115" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B116" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C116" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D116" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E116" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B117" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C117" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D117" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E117" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B118" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C118" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D118" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E118" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B119" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C119" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D119" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C120" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D120" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E120" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B121" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C121" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D121" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E121" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B122" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C122" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D122" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E122" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B123" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C123" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D123" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E123" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B124" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C124" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D124" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E124" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B125" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C125" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D125" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E125" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B126" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C126" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D126" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E126" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B127" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C127" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D127" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E127" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B128" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C128" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D128" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B129" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C129" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D129" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E129" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B130" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C130" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D130" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E130" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B131" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C131" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D131" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E131" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B132" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C132" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D132" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E132" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C133" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D133" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B134" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C134" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D134" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E134" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B135" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C135" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D135" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E135" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B136" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D136" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E136" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B137" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C137" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D137" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E137" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B138" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C138" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D138" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E138" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B139" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D139" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E139" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B140" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C140" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D140" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E140" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C141" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D141" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E141" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B142" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C142" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D142" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E142" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>310</v>
+      </c>
+      <c r="B143" t="s">
         <v>320</v>
       </c>
-      <c r="B143" t="s">
-        <v>330</v>
-      </c>
       <c r="C143" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D143" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E143" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B144" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D144" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E144" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B145" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D145" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E145" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D146" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E146" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B147" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C147" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D147" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E147" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B148" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C148" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E148" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C149" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D149" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E149" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D150" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E150" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C151" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D151" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B152" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C152" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D152" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E152" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B153" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C153" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D153" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E153" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B154" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C154" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D154" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E154" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C155" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D155" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E155" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B156" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C156" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D156" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E156" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C157" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D157" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E157" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B158" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C158" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D158" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E158" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C159" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D159" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E159" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B160" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C160" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D160" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E160" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B161" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C161" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D161" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E161" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B162" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C162" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E162" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B163" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C163" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D163" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E163" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B164" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C164" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D164" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E164" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C165" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D165" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E165" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B166" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C166" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D166" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E166" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B167" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C167" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D167" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E167" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B168" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C168" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D168" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E168" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B169" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C169" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D169" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E169" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B170" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C170" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D170" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E170" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B171" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C171" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E171" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B172" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C172" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D172" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E172" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B173" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C173" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D173" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E173" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B174" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C174" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D174" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E174" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B175" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C175" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D175" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E175" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B176" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D176" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E176" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B177" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C177" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E177" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B178" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C178" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D178" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E178" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B179" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C179" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D179" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E179" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B180" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C180" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D180" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E180" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B181" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C181" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D181" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B182" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C182" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D182" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E182" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B183" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C183" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D183" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E183" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B184" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C184" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E184" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B185" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C185" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D185" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E185" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B186" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C186" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D186" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E186" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B187" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C187" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E187" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B188" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C188" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D188" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E188" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B189" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C189" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D189" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E189" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B190" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C190" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D190" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E190" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B191" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C191" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E191" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B192" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C192" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D192" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E192" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B193" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C193" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D193" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E193" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B194" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C194" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D194" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E194" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B195" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C195" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D195" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E195" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B196" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C196" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D196" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E196" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B197" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C197" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D197" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E197" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B198" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C198" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D198" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E198" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B199" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C199" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D199" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E199" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B200" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C200" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D200" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E200" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B201" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C201" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D201" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E201" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B202" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C202" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D202" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E202" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B203" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C203" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D203" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E203" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B204" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C204" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D204" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E204" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B205" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C205" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D205" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E205" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B206" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C206" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D206" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E206" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B207" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C207" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D207" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E207" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B208" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C208" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D208" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E208" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B209" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C209" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D209" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E209" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B210" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C210" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D210" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E210" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B211" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C211" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D211" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E211" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B212" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C212" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D212" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E212" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B213" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C213" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D213" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E213" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B214" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C214" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D214" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E214" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B215" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C215" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D215" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E215" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B216" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C216" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D216" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E216" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B217" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C217" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D217" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E217" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B218" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C218" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D218" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E218" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B219" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C219" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E219" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B220" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C220" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D220" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E220" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B221" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C221" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E221" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B222" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C222" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E222" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B223" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C223" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E223" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
+        <v>357</v>
+      </c>
+      <c r="B224" t="s">
         <v>367</v>
       </c>
-      <c r="B224" t="s">
-        <v>377</v>
-      </c>
       <c r="C224" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D224" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E224" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B225" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C225" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D225" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E225" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B226" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C226" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D226" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E226" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B227" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C227" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E227" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B228" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C228" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D228" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E228" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B229" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C229" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E229" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B230" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C230" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D230" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E230" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B231" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C231" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D231" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E231" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B232" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C232" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D232" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E232" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B233" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C233" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E233" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B234" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C234" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D234" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E234" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B235" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C235" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E235" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B236" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C236" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D236" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E236" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B237" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C237" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D237" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E237" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B238" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C238" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D238" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E238" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B239" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C239" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D239" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E239" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B240" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C240" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D240" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E240" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B241" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C241" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E241" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B242" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C242" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D242" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E242" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B243" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C243" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D243" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E243" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B244" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C244" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E244" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B245" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C245" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D245" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E245" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B246" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C246" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D246" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E246" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B247" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C247" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E247" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B248" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C248" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D248" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E248" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B249" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C249" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D249" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E249" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B250" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C250" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D250" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E250" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B251" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C251" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D251" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E251" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B252" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C252" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D252" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E252" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B253" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C253" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E253" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B254" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C254" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D254" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E254" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B255" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C255" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D255" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E255" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B256" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C256" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E256" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B257" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C257" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D257" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E257" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B258" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C258" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D258" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E258" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B259" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C259" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D259" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E259" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B260" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C260" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D260" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E260" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/reference/dictionaries/EE.xlsx
+++ b/reference/dictionaries/EE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Documents\Development\EHR-BSI\reference\dictionaries\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j.humphreys\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E279AC-9E1B-4F03-91A6-71DE8EE35523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E9EF75-877B-4A77-9666-B48C0330E7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="402">
   <si>
     <t>raw_column_name</t>
   </si>
@@ -30,9 +30,6 @@
     <t>standard_column_name</t>
   </si>
   <si>
-    <t>PATIENT_ID_HASH</t>
-  </si>
-  <si>
     <t>PatientId</t>
   </si>
   <si>
@@ -48,9 +45,6 @@
     <t>Sex</t>
   </si>
   <si>
-    <t>L1_PROC_TIME (sample collection date)</t>
-  </si>
-  <si>
     <t>L1_PROC_ARTICLE_CODE_NAME</t>
   </si>
   <si>
@@ -75,10 +69,6 @@
     <t>sensitivityTest_noncdm</t>
   </si>
   <si>
-    <t>L3_RSLT_CODE_NAME
-(SIR)</t>
-  </si>
-  <si>
     <t>sensitivityResult_noncdm</t>
   </si>
   <si>
@@ -94,45 +84,24 @@
     <t>sensitivityValue_noncdm</t>
   </si>
   <si>
-    <t>SAMPLE_CONTEINER_ID (Isolate ID)</t>
-  </si>
-  <si>
     <t>IsolateId</t>
   </si>
   <si>
-    <t>Hosital ID</t>
-  </si>
-  <si>
     <t>HospitalId</t>
   </si>
   <si>
-    <t>STAT_EPICRISIS_CASE_START (admission date)</t>
-  </si>
-  <si>
     <t>DateOfHospitalAdmission</t>
   </si>
   <si>
-    <t>STAT_EPICRISIS_CASE_END (discharge date)</t>
-  </si>
-  <si>
     <t>DateOfHospitalDischarge</t>
   </si>
   <si>
-    <t>Unit ID</t>
-  </si>
-  <si>
     <t>UnitSpecialtyShort</t>
   </si>
   <si>
-    <t>BED_START_TIME (unit admission date)</t>
-  </si>
-  <si>
     <t>DateOfAdmissionCurrentWard</t>
   </si>
   <si>
-    <t>BED_END_TIME (unit discharge date)</t>
-  </si>
-  <si>
     <t>DateOfDischargeCurrentWard</t>
   </si>
   <si>
@@ -1223,6 +1192,42 @@
   </si>
   <si>
     <t>EE009</t>
+  </si>
+  <si>
+    <t>PATIENT_ID</t>
+  </si>
+  <si>
+    <t>L1_PROC_TIME</t>
+  </si>
+  <si>
+    <t>L3_RSLT_CODE_NAME</t>
+  </si>
+  <si>
+    <t>SAMPLE_CONTEINER_ID</t>
+  </si>
+  <si>
+    <t>Hospital ID</t>
+  </si>
+  <si>
+    <t>CASE_START</t>
+  </si>
+  <si>
+    <t>CASE_END</t>
+  </si>
+  <si>
+    <t>UNIT ID</t>
+  </si>
+  <si>
+    <t>BED_START_TIME</t>
+  </si>
+  <si>
+    <t>BED_END_TIME</t>
+  </si>
+  <si>
+    <t>Lab ID</t>
+  </si>
+  <si>
+    <t>LaboratoryId</t>
   </si>
 </sst>
 </file>
@@ -1556,8 +1561,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="49.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1569,154 +1577,162 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>391</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>393</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>394</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>395</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>396</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>397</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>398</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>399</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>400</v>
+      </c>
+      <c r="B21" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -1736,356 +1752,356 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2105,4439 +2121,4439 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
         <v>103</v>
       </c>
-      <c r="B7" t="s">
-        <v>113</v>
-      </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C22" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>148</v>
-      </c>
       <c r="C24" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B28" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D29" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B31" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E31" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B33" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E35" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E37" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E39" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C40" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" t="s">
         <v>164</v>
       </c>
-      <c r="B41" t="s">
-        <v>174</v>
-      </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E41" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C42" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E42" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C45" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E45" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B46" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C46" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E46" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B47" t="s">
+        <v>162</v>
+      </c>
+      <c r="C47" t="s">
         <v>172</v>
       </c>
-      <c r="C47" t="s">
-        <v>182</v>
-      </c>
       <c r="D47" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B48" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D48" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D49" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B50" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C50" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C51" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D51" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B52" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C53" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D53" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C54" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B55" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C55" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D55" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E55" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E56" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C57" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" t="s">
         <v>174</v>
-      </c>
-      <c r="C57" t="s">
-        <v>182</v>
-      </c>
-      <c r="D57" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E58" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C59" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D59" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E59" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E60" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D61" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E61" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C62" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E62" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C63" t="s">
+        <v>177</v>
+      </c>
+      <c r="D63" t="s">
         <v>173</v>
       </c>
-      <c r="C63" t="s">
-        <v>187</v>
-      </c>
-      <c r="D63" t="s">
-        <v>183</v>
-      </c>
       <c r="E63" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C64" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D64" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E64" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B65" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C65" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B66" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C66" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D66" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E66" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C67" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E67" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>180</v>
+      </c>
+      <c r="B68" t="s">
         <v>190</v>
       </c>
-      <c r="B68" t="s">
-        <v>200</v>
-      </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B69" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D69" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E69" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="D70" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E70" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B71" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B72" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="D72" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E72" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C73" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B74" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B75" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D75" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E75" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B76" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C76" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E76" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B77" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D77" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E77" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B78" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C78" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D78" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E78" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D79" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E79" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B80" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C80" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D80" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E80" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B81" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C81" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E81" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C82" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D82" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E82" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C83" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D83" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E83" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C84" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D84" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C85" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D85" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E85" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C86" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E86" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B87" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E87" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C88" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D88" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C89" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D89" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E89" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B90" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C90" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D90" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E90" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D91" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B92" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C92" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D92" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E92" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C93" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D93" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C94" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D94" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E94" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B95" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C95" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D95" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E95" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D96" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E96" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C97" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D97" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E97" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C98" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D98" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C99" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D99" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E99" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C100" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D100" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="C101" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D101" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E101" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C102" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D102" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B103" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C103" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E103" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B104" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C104" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D104" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="C105" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D105" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E105" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B106" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="C106" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D106" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E106" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B107" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C107" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D107" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E107" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B108" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C108" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D108" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E108" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B109" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="C109" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D109" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E109" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B110" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C110" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D110" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E110" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B111" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C111" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D111" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E111" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="C112" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D112" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E112" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B113" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="C113" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D113" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E113" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C114" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D114" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C115" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="D115" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E115" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B116" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="C116" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D116" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E116" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="C117" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D117" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E117" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B118" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C118" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D118" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E118" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B119" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C119" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D119" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B120" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C120" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D120" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E120" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C121" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D121" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E121" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B122" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C122" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D122" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E122" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B123" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C123" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D123" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E123" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B124" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C124" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D124" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E124" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B125" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C125" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D125" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E125" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B126" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C126" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D126" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E126" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B127" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C127" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D127" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E127" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B128" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="C128" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D128" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E128" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B129" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C129" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D129" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="E129" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B130" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="C130" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="D130" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E130" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B131" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="C131" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D131" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E131" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B132" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="C132" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D132" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E132" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B133" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="C133" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D133" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E133" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B134" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C134" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D134" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E134" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B135" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C135" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D135" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E135" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B136" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C136" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D136" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E136" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B137" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C137" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D137" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E137" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B138" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="C138" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D138" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E138" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B139" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C139" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D139" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E139" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B140" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C140" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D140" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E140" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B141" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C141" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D141" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E141" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B142" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C142" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D142" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E142" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B143" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C143" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D143" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E143" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
+        <v>310</v>
+      </c>
+      <c r="B144" t="s">
         <v>320</v>
       </c>
-      <c r="B144" t="s">
-        <v>330</v>
-      </c>
       <c r="C144" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D144" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E144" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B145" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="C145" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D145" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E145" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B146" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C146" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="D146" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E146" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B147" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C147" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D147" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E147" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B148" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C148" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="D148" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E148" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B149" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C149" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D149" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E149" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B150" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="C150" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D150" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E150" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C151" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D151" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E151" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B152" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C152" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D152" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E152" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B153" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="C153" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D153" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E153" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B154" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="C154" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="D154" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E154" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B155" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C155" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="D155" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E155" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B156" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C156" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D156" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E156" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B157" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C157" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D157" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E157" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B158" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C158" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D158" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E158" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="C159" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D159" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E159" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B160" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C160" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D160" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E160" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B161" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="C161" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D161" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E161" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B162" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="C162" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E162" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B163" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C163" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D163" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E163" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B164" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C164" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D164" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E164" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B165" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C165" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="D165" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E165" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B166" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="C166" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D166" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E166" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B167" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C167" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D167" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E167" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B168" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C168" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D168" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E168" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B169" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C169" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D169" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E169" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B170" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C170" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D170" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E170" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B171" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C171" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E171" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B172" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C172" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D172" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E172" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B173" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C173" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D173" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E173" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B174" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C174" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D174" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E174" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B175" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C175" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D175" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E175" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B176" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C176" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D176" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E176" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B177" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E177" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B178" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C178" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D178" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E178" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B179" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C179" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D179" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E179" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B180" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C180" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D180" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E180" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B181" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="D181" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B182" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C182" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D182" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E182" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B183" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C183" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="D183" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E183" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B184" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C184" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D184" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E184" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B185" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C185" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D185" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E185" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B186" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C186" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D186" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E186" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B187" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C187" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D187" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E187" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B188" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="C188" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D188" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E188" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B189" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C189" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D189" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E189" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B190" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C190" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D190" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E190" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B191" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C191" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D191" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E191" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B192" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C192" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E192" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B193" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C193" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D193" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E193" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B194" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C194" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="D194" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E194" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B195" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C195" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="D195" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E195" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B196" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C196" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="D196" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E196" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B197" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C197" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D197" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E197" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B198" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C198" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="D198" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E198" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B199" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C199" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="D199" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E199" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B200" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C200" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D200" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E200" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B201" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C201" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D201" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E201" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B202" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C202" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D202" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E202" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B203" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C203" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D203" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E203" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B204" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C204" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="D204" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E204" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B205" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C205" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D205" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E205" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B206" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="C206" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D206" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E206" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B207" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C207" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D207" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E207" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B208" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C208" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D208" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E208" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B209" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C209" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D209" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E209" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B210" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C210" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="D210" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E210" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B211" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C211" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D211" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E211" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B212" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="C212" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D212" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E212" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B213" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C213" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D213" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E213" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B214" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C214" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D214" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E214" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B215" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C215" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D215" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E215" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B216" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C216" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D216" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E216" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B217" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="C217" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="D217" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E217" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B218" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C218" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D218" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E218" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B219" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C219" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D219" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E219" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B220" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C220" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="D220" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E220" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B221" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C221" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D221" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E221" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B222" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C222" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D222" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E222" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B223" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C223" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D223" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E223" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B224" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C224" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D224" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E224" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
+        <v>357</v>
+      </c>
+      <c r="B225" t="s">
         <v>367</v>
       </c>
-      <c r="B225" t="s">
-        <v>377</v>
-      </c>
       <c r="C225" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D225" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E225" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B226" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C226" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D226" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E226" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B227" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C227" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D227" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E227" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B228" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C228" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D228" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E228" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B229" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C229" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D229" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E229" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B230" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C230" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D230" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E230" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B231" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C231" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D231" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E231" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B232" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C232" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D232" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E232" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B233" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C233" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D233" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E233" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B234" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C234" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D234" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E234" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B235" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C235" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D235" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E235" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B236" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C236" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D236" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E236" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B237" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C237" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D237" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E237" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B238" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C238" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="D238" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E238" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B239" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C239" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="D239" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E239" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B240" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C240" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D240" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E240" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B241" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="C241" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D241" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E241" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B242" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C242" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D242" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E242" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B243" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="C243" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D243" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E243" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B244" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C244" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D244" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E244" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B245" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C245" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D245" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E245" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B246" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C246" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D246" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E246" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B247" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C247" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D247" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E247" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B248" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C248" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D248" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E248" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B249" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C249" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D249" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E249" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B250" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C250" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D250" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E250" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B251" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C251" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D251" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E251" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B252" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C252" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D252" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E252" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B253" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C253" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D253" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E253" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B254" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C254" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D254" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E254" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B255" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C255" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D255" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E255" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B256" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C256" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D256" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E256" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B257" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C257" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D257" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E257" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B258" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C258" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D258" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E258" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B259" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C259" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D259" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E259" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B260" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C260" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D260" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E260" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B261" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C261" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="D261" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E261" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
